--- a/out/Attention-mamba2_repeat_3_000007.xlsx
+++ b/out/Attention-mamba2_repeat_3_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542421</v>
+        <v>5.448042895279976</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542421</v>
+        <v>5.448042895279976</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542421</v>
+        <v>6.048042895279975</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.50126221553543</v>
+        <v>6.048042895279975</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5903981995424212</v>
+        <v>6.048042895279975</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5903981995424212</v>
+        <v>6.048042895279975</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542421</v>
+        <v>6.048042895279975</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.04098559548271047</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.04098559548271047</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC39" t="n">
-        <v>-5.497734545799904e-05</v>
+        <v>-5.1119644884835e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.6338075967963034</v>
+        <v>0.5893340066480393</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.268594945754792</v>
+        <v>1.179579017313987</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.09504227641307941</v>
+        <v>0.08837326318364065</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.8240212448095158</v>
+        <v>0.7662005697334192</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1188337702731704</v>
+        <v>0.1104952770391442</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.9666616023190853</v>
+        <v>0.8988320084949735</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1703476461291206</v>
+        <v>0.158394618297549</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.188590187460401</v>
+        <v>1.105188212009103</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1822378908731438</v>
+        <v>0.1694508668064311</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.382731720544362</v>
+        <v>1.285707136942438</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1931361703240452</v>
+        <v>0.1795837644107526</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.586779264191532</v>
+        <v>1.475436621302852</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.08715876157112856</v>
+        <v>0.08104214697792185</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.567800121619535</v>
+        <v>1.45778925018872</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04209369811331787</v>
+        <v>0.03914029599657854</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.564760411896289</v>
+        <v>1.454962814317222</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02005639394182798</v>
+        <v>0.01864918576157993</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.562746073434523</v>
+        <v>1.453089807022435</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.005939387333039069</v>
+        <v>0.005522313829901992</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.554550272598968</v>
+        <v>1.445468693838708</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003926504718406224</v>
+        <v>0.003650626514449602</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.556462374248331</v>
+        <v>1.447246286746994</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002007188215154658</v>
+        <v>0.001866482633361447</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.556547930499486</v>
+        <v>1.447325489558267</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001024815366621832</v>
+        <v>0.0009523356927246939</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.556588191484618</v>
+        <v>1.44736256501952</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003817681926805059</v>
+        <v>0.0003545203356619184</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.556326889655834</v>
+        <v>1.44711930206168</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002062015301782022</v>
+        <v>0.0001913514225875474</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.556356551759197</v>
+        <v>1.447146526985901</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>9.672543367146604e-05</v>
+        <v>8.95728641164411e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.556343667548747</v>
+        <v>1.447134197133999</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.797312751584259e-05</v>
+        <v>5.305335192866738e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.556362840802238</v>
+        <v>1.44715167130457</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.793981303953445e-05</v>
+        <v>2.588107472456355e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.556360710712908</v>
+        <v>1.447149361845824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.098549009256284e-05</v>
+        <v>9.986396961777667e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.556354721258114</v>
+        <v>1.447143434231955</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.233171022101693e-06</v>
+        <v>3.954024644338981e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.556354195072836</v>
+        <v>1.447142629209551</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.556348280036055</v>
+        <v>1.44713671417277</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.556342731907834</v>
+        <v>1.447131166044549</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.556337897273516</v>
+        <v>1.447126331410231</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.556337753289608</v>
+        <v>1.447126187426323</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.556337730555307</v>
+        <v>1.447126164692022</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.556338048835523</v>
+        <v>1.447126482972238</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.556339140081981</v>
+        <v>1.447127574218696</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.556338450474845</v>
+        <v>1.447126884611559</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.556338480787246</v>
+        <v>1.447126914923961</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.556338291334736</v>
+        <v>1.447126725471451</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.556338344381439</v>
+        <v>1.447126778518154</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.556338397428142</v>
+        <v>1.447126831564857</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.55633835953764</v>
+        <v>1.447126793674354</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.556338230709933</v>
+        <v>1.447126664846648</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.556338086726026</v>
+        <v>1.44712652086274</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.556337927585917</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.55633798063262</v>
+        <v>1.447126414769335</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.556337927585917</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.556337927585917</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.556337745711508</v>
+        <v>1.447126179848222</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.556337912429717</v>
+        <v>1.447126346566431</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.556338109460327</v>
+        <v>1.447126543597042</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.556337950320219</v>
+        <v>1.447126384456934</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.55633798821072</v>
+        <v>1.447126422347435</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.556338185241331</v>
+        <v>1.447126619378046</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.55633816250703</v>
+        <v>1.447126596643745</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.556338010945022</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.556337935164018</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.556338033679323</v>
+        <v>1.447126467816038</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.556338041257423</v>
+        <v>1.447126475394138</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.556338306490937</v>
+        <v>1.447126740627652</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.556338010945022</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.556338253444234</v>
+        <v>1.447126687580949</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.556338336803339</v>
+        <v>1.447126770940053</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.55633817008513</v>
+        <v>1.447126604221844</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.55633835953764</v>
+        <v>1.447126793674354</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.556338010945022</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.556337806336311</v>
+        <v>1.447126240473026</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.556337920007817</v>
+        <v>1.447126354144532</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.556337935164018</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.556337700242906</v>
+        <v>1.44712613437962</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.556337760867708</v>
+        <v>1.447126195004423</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.556337632040002</v>
+        <v>1.447126066176717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.556337768445809</v>
+        <v>1.447126202582524</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.556337942742118</v>
+        <v>1.447126376878833</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.556338086726026</v>
+        <v>1.44712652086274</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.556337920007817</v>
+        <v>1.447126354144532</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.556337912429717</v>
+        <v>1.447126346566431</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.556337624461901</v>
+        <v>1.447126058598616</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.556337639618103</v>
+        <v>1.447126073754817</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.556337866961114</v>
+        <v>1.447126301097829</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.556337851804914</v>
+        <v>1.447126285941628</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.556337957898319</v>
+        <v>1.447126392035033</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.556337685086705</v>
+        <v>1.447126119223419</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.55633778360201</v>
+        <v>1.447126217738725</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.556337935164018</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.556337950320219</v>
+        <v>1.447126384456934</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.556337927585917</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.556338010945022</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.556338109460327</v>
+        <v>1.447126543597042</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.556337942742118</v>
+        <v>1.447126376878833</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.556337927585917</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.556337897273516</v>
+        <v>1.447126331410231</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.556337882117315</v>
+        <v>1.44712631625403</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.556337920007817</v>
+        <v>1.447126354144532</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.556337935164018</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.6409855954827104</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.556337927585917</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000007.xlsx
+++ b/out/Attention-mamba2_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765016995</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.50126221553543</v>
+        <v>0.03851195765016993</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC39" t="n">
-        <v>-5.497734545799904e-05</v>
+        <v>-6.473156040150206e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.6338075967963034</v>
+        <v>0.7462592890442209</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.268594945754792</v>
+        <v>1.493672160272826</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.09504227641307941</v>
+        <v>0.1119048865970657</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.8240212448095158</v>
+        <v>0.9702211072335367</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1188337702731704</v>
+        <v>0.1399175764823317</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.9666616023190853</v>
+        <v>1.138169099504032</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1703476461291206</v>
+        <v>0.200571019667155</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.188590187460401</v>
+        <v>1.399472849641365</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1822378908731438</v>
+        <v>0.2145712619793919</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.382731720544362</v>
+        <v>1.628059679474607</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1931361703240452</v>
+        <v>0.2274030266038829</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.586779264191532</v>
+        <v>1.868310011241062</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.08715876157112856</v>
+        <v>0.1026227564886806</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.567800121619535</v>
+        <v>1.845963526602905</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04209369811331787</v>
+        <v>0.04956210085277282</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.50126221553543</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.564760411896289</v>
+        <v>1.842384501555947</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02005639394182798</v>
+        <v>0.02361486549867473</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.562746073434523</v>
+        <v>1.840012772521237</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.005939387333039069</v>
+        <v>0.006993696833129484</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.554550272598968</v>
+        <v>1.83036373323349</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003926504718406224</v>
+        <v>0.004624370837125765</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.556462374248331</v>
+        <v>1.832616090443907</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002007188215154658</v>
+        <v>0.002364363922783577</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.556547930499486</v>
+        <v>1.832717716947686</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001024815366621832</v>
+        <v>0.001207021213502136</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.556588191484618</v>
+        <v>1.832766008720208</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003817681926805059</v>
+        <v>0.0004506447201441577</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.556326889655834</v>
+        <v>1.832459108634311</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002062015301782022</v>
+        <v>0.0002433267991548393</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.556356551759197</v>
+        <v>1.832494931888435</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>9.672543367146604e-05</v>
+        <v>0.0001150042225343076</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.556343667548747</v>
+        <v>1.83248063098392</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.797312751584259e-05</v>
+        <v>6.879663380762803e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765016995</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.556362840802238</v>
+        <v>1.832504148467864</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.793981303953445e-05</v>
+        <v>3.411602798444717e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.50126221553543</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.556360710712908</v>
+        <v>1.832502556486785</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.098549009256284e-05</v>
+        <v>1.398276948491838e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.556354721258114</v>
+        <v>1.832496381509218</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.233171022101693e-06</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.556354195072836</v>
+        <v>1.832496694940494</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.375548894532629e-07</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.50126221553543</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.556348280036055</v>
+        <v>1.832490551144519</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.556342731907834</v>
+        <v>1.832484866610491</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.556337897273516</v>
+        <v>1.832480115335277</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.556337753289608</v>
+        <v>1.832474826187715</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.556337730555307</v>
+        <v>1.832474803453414</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.556338048835523</v>
+        <v>1.83247512173363</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.556339140081981</v>
+        <v>1.832476212980087</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.556338450474845</v>
+        <v>1.832475523372951</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.556338480787246</v>
+        <v>1.832475553685353</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.556338291334736</v>
+        <v>1.832475364232843</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.556338344381439</v>
+        <v>1.832475417279546</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>2.50126221553543</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.556338397428142</v>
+        <v>1.832475470326248</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.55633835953764</v>
+        <v>1.832475432435746</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.556338230709933</v>
+        <v>1.83247530360804</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.556338086726026</v>
+        <v>1.832475159624132</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.556337927585917</v>
+        <v>1.832475000484024</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765016995</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.55633798063262</v>
+        <v>1.832475053530727</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.50126221553543</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.556337927585917</v>
+        <v>1.832475000484024</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.556337927585917</v>
+        <v>1.832475000484024</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.556337745711508</v>
+        <v>1.832474818609614</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.556337912429717</v>
+        <v>1.832474985327823</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765016995</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.556338109460327</v>
+        <v>1.832475182358434</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.50126221553543</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.556337950320219</v>
+        <v>1.832475023218325</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.55633798821072</v>
+        <v>1.832475061108827</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.556338185241331</v>
+        <v>1.832475258139437</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765016995</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.55633816250703</v>
+        <v>1.832475235405136</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.556338010945022</v>
+        <v>1.832475083843128</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.556337935164018</v>
+        <v>1.832475008062124</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.23851195765017</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.556338033679323</v>
+        <v>1.832475106577429</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5903981995424212</v>
+        <v>-0.4624876642263468</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.556338041257423</v>
+        <v>1.83247511415553</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.556338306490937</v>
+        <v>1.832475379389044</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.556338010945022</v>
+        <v>1.832475083843128</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.556338253444234</v>
+        <v>1.832475326342341</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.556338336803339</v>
+        <v>1.832475409701445</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.55633817008513</v>
+        <v>1.832475242983236</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542421</v>
+        <v>-0.6624876642263469</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.55633835953764</v>
+        <v>1.832475432435746</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765016995</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.556338010945022</v>
+        <v>1.832475083843128</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.556337806336311</v>
+        <v>1.832474879234418</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.556337920007817</v>
+        <v>1.832474992905924</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.556337935164018</v>
+        <v>1.832475008062124</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.556337700242906</v>
+        <v>1.832474773141012</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.556337760867708</v>
+        <v>1.832474833765815</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.556337632040002</v>
+        <v>1.832474704938108</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5903981995424212</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.556337768445809</v>
+        <v>1.832474841343916</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9395115795266867</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.556337942742118</v>
+        <v>1.832475015640225</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7395115795266867</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.556338086726026</v>
+        <v>1.832475159624132</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765017004</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.556337920007817</v>
+        <v>1.832474992905924</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542421</v>
+        <v>0.03851195765017004</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.556337912429717</v>
+        <v>1.832474985327823</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7395115795266867</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.556337624461901</v>
+        <v>1.832474697360008</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.556337639618103</v>
+        <v>1.832474712516209</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.556337866961114</v>
+        <v>1.832474939859221</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.556337851804914</v>
+        <v>1.83247492470302</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.556337957898319</v>
+        <v>1.832475030796425</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.556337685086705</v>
+        <v>1.832474757984812</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.55633778360201</v>
+        <v>1.832474856500117</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.556337935164018</v>
+        <v>1.832475008062124</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.50126221553543</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.556337950320219</v>
+        <v>1.832475023218325</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.901262215535431</v>
+        <v>1.640511201403204</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.556337927585917</v>
+        <v>1.832475000484024</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.556338010945022</v>
+        <v>1.832475083843128</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.556338109460327</v>
+        <v>1.832475182358434</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.556337942742118</v>
+        <v>1.832475015640225</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.556337927585917</v>
+        <v>1.832475000484024</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.556337897273516</v>
+        <v>1.832474970171623</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.556337882117315</v>
+        <v>1.832474955015421</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.556337920007817</v>
+        <v>1.832474992905924</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.556337935164018</v>
+        <v>1.832475008062124</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.901262215535431</v>
+        <v>1.440511201403203</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.556337927585917</v>
+        <v>1.832475000484024</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000007.xlsx
+++ b/out/Attention-mamba2_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.18976691365242</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.2035084515810013</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.1960236132144928</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.03851195765016995</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.09563732147216797</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.03851195765016993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.3741496205329895</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.2842496037483215</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.2225941568613052</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.242017075419426</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2307475358247757</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.2361661940813065</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.218928650021553</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.2092815488576889</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.232180044054985</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2396268993616104</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.273548036813736</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.2371569126844406</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.231830433011055</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.2217520922422409</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.245067372918129</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.2396668642759323</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.2729325294494629</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.387547105550766</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.3150195777416229</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.2576042413711548</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.2356085032224655</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2229620367288589</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2103167325258255</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.2543826997280121</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2702330350875854</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2326614409685135</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.2174177914857864</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2233928591012955</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.2273466140031815</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.2355862110853195</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.3873419463634491</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.23851195765017</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.006749171763658524</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.23851195765017</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.02970215305685997</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.23851195765017</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.03456762805581093</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4624876642263468</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.473156040150206e-05</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.7462592890442209</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.03901778534054756</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4624876642263468</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.493672160272826</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1119048865970657</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.04738070443272591</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9702211072335367</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1399175764823317</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0381372906267643</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.138169099504032</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.200571019667155</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.04041441902518272</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.16</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.399472849641365</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2145712619793919</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.05144154652953148</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.628059679474607</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2274030266038829</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0557393841445446</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.868310011241062</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1026227564886806</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.06797398626804352</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.845963526602905</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04956210085277282</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.05239151418209076</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.842384501555947</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02361486549867473</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.06835545599460602</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.840012772521237</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006993696833129484</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0205792635679245</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.23851195765017</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.83036373323349</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004624370837125765</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.009337387979030609</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.23851195765017</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.832616090443907</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002364363922783577</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0006307028234004974</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4624876642263468</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.832717716947686</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001207021213502136</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.03204232826828957</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.832766008720208</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004506447201441577</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.02797854319214821</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.832459108634311</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002433267991548393</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.008544843643903732</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.832494931888435</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001150042225343076</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.006154913455247879</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.83248063098392</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.879663380762803e-05</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01526877656579018</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.03851195765016995</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.832504148467864</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.411602798444717e-05</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.009026631712913513</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.832502556486785</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.398276948491838e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.04134514555335045</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.832496381509218</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.03339111432433128</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.23851195765017</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.832496694940494</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.280563881834207e-07</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001816079020500183</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.832490551144519</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003373067826032639</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.23851195765017</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.832484866610491</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02251827344298363</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4624876642263468</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.832480115335277</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.02007193490862846</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.832474826187715</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01400273665785789</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.832474803453414</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.06228164210915565</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.83247512173363</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.07285945117473602</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.832476212980087</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.06370654702186584</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.832475523372951</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0455504022538662</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.832475553685353</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.01346650347113609</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.832475364232843</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006745383143424988</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.23851195765017</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.832475417279546</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.006663687527179718</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.23851195765017</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.832475470326248</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0008146762847900391</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.23851195765017</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.832475432435746</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01451227441430092</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4624876642263468</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.83247530360804</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01525947079062462</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4624876642263468</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.832475159624132</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.008551470935344696</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6624876642263469</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.832475000484024</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004303105175495148</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.03851195765016995</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.832475053530727</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.007537800818681717</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.832475000484024</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004317298531532288</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.832475000484024</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02293415740132332</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4624876642263468</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.832474818609614</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02588210627436638</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.832474985327823</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0002718828618526459</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.03851195765016995</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.832475182358434</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.004726890474557877</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.832475023218325</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01494292542338371</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.23851195765017</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.832475061108827</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0421680323779583</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4624876642263468</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.832475258139437</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.00518205389380455</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.03851195765016995</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.832475235405136</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.006607722491025925</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.832475083843128</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.005217641592025757</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.832475008062124</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003978181630373001</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.23851195765017</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.832475106577429</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.03644482418894768</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4624876642263468</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.83247511415553</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01816165074706078</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.832475379389044</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002157367765903473</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.832475083843128</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02815261110663414</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.832475326342341</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.001547202467918396</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.832475409701445</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.04984831437468529</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.832475242983236</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01966977491974831</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6624876642263469</v>
+        <v>-0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.832475432435746</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01001979410648346</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.03851195765016995</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.832475083843128</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01591142266988754</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.832474879234418</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01250101253390312</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.832474992905924</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.006860498338937759</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.832475008062124</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.002010758966207504</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.832474773141012</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01718297228217125</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.640511201403204</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.832474833765815</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.006900142878293991</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9395115795266867</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.832474704938108</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.03814482316374779</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9395115795266867</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.832474841343916</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01467718929052353</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9395115795266867</v>
+        <v>-0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.832475015640225</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.00669398158788681</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7395115795266867</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.832475159624132</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>3.174319863319397e-05</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.03851195765017004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.832474992905924</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004581909626722336</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.03851195765017004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.832474985327823</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0129743367433548</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7395115795266867</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.832474697360008</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.02671688608825207</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.440511201403203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.832474712516209</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.02534761279821396</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.640511201403204</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.832474939859221</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01801422983407974</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.640511201403204</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.83247492470302</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0169435515999794</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.640511201403204</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.832475030796425</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.01825009286403656</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.640511201403204</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.832474757984812</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.02937855571508408</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.640511201403204</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.832474856500117</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.02354414388537407</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.640511201403204</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.832475008062124</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.01849814876914024</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.640511201403204</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.832475023218325</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01562341675162315</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.640511201403204</v>
+        <v>-0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.832475000484024</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01121670007705688</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.440511201403203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.832475083843128</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01570022851228714</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.440511201403203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.832475182358434</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.02089432999491692</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.440511201403203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.832475015640225</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.02230215072631836</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.440511201403203</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.832475000484024</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0207916833460331</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.440511201403203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.832474970171623</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01999262720346451</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.440511201403203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.832474955015421</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.01728371158242226</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.440511201403203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.832474992905924</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01271422207355499</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.440511201403203</v>
+        <v>0.7899999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.832475008062124</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.03012174367904663</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.440511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.832475000484024</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000007.xlsx
+++ b/out/Attention-mamba2_repeat_3_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.18976691365242</v>
+        <v>-0.1893815249204636</v>
       </c>
       <c r="JB2" t="n">
         <v>-1</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.2035084515810013</v>
+        <v>-0.2031926959753036</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.1960236132144928</v>
+        <v>-0.1955235600471497</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.09563732147216797</v>
+        <v>0.09481406211853027</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.3741496205329895</v>
+        <v>-0.3742267787456512</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.2842496037483215</v>
+        <v>-0.284017413854599</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.2225941568613052</v>
+        <v>-0.2222615033388138</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.242017075419426</v>
+        <v>-0.2417578846216202</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2307475358247757</v>
+        <v>-0.2304426282644272</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.2361661940813065</v>
+        <v>-0.2358885556459427</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.218928650021553</v>
+        <v>-0.2186244279146194</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.2092815488576889</v>
+        <v>-0.2089496999979019</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.232180044054985</v>
+        <v>-0.2318998128175735</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2396268993616104</v>
+        <v>-0.2393250316381454</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.273548036813736</v>
+        <v>-0.273378849029541</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.2371569126844406</v>
+        <v>-0.2368888407945633</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.2599999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.231830433011055</v>
+        <v>-0.2315680235624313</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.2599999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.2217520922422409</v>
+        <v>-0.2214550524950027</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.2599999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.245067372918129</v>
+        <v>-0.2448561042547226</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.2599999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.2396668642759323</v>
+        <v>-0.2394035309553146</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.2599999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.2729325294494629</v>
+        <v>-0.2726313173770905</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.387547105550766</v>
+        <v>-0.3876688778400421</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.3150195777416229</v>
+        <v>-0.3148719072341919</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.2576042413711548</v>
+        <v>-0.257346123456955</v>
       </c>
       <c r="JB25" t="n">
         <v>0.02000000000000007</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.2356085032224655</v>
+        <v>-0.2353179305791855</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2229620367288589</v>
+        <v>-0.2226636558771133</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2103167325258255</v>
+        <v>-0.2099699825048447</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.2543826997280121</v>
+        <v>-0.2541154623031616</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2702330350875854</v>
+        <v>-0.2699815332889557</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2326614409685135</v>
+        <v>-0.2323734015226364</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.2174177914857864</v>
+        <v>-0.2170934230089188</v>
       </c>
       <c r="JB32" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2233928591012955</v>
+        <v>-0.2230962067842484</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.2273466140031815</v>
+        <v>-0.2270461469888687</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.2355862110853195</v>
+        <v>-0.2351578027009964</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.3873419463634491</v>
+        <v>-0.3870846331119537</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.006749171763658524</v>
+        <v>0.006886240094900131</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.02970215305685997</v>
+        <v>-0.03000236675143242</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.03456762805581093</v>
+        <v>-0.03492515161633492</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.03901778534054756</v>
+        <v>-0.03946204110980034</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.04738070443272591</v>
+        <v>-0.047868762165308</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0381372906267643</v>
+        <v>-0.04106111451983452</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.02000000000000007</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.04041441902518272</v>
+        <v>-0.04098780825734138</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.16</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.05144154652953148</v>
+        <v>-0.05190915986895561</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.3</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0557393841445446</v>
+        <v>-0.05644184723496437</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.06797398626804352</v>
+        <v>-0.06858371198177338</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.16</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.05239151418209076</v>
+        <v>0.008259203284978867</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.02000000000000007</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.06835545599460602</v>
+        <v>-0.06870885193347931</v>
       </c>
       <c r="JB48" t="n">
         <v>0.1199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.0205792635679245</v>
+        <v>0.004103183746337891</v>
       </c>
       <c r="JB49" t="n">
         <v>0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.009337387979030609</v>
+        <v>-0.03589724376797676</v>
       </c>
       <c r="JB50" t="n">
         <v>0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0006307028234004974</v>
+        <v>-0.001323863863945007</v>
       </c>
       <c r="JB51" t="n">
         <v>0.8599999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.03204232826828957</v>
+        <v>-0.03298266604542732</v>
       </c>
       <c r="JB52" t="n">
         <v>0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.02797854319214821</v>
+        <v>-0.02886490896344185</v>
       </c>
       <c r="JB53" t="n">
         <v>0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.008544843643903732</v>
+        <v>-0.009227462112903595</v>
       </c>
       <c r="JB54" t="n">
         <v>0.5799999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.006154913455247879</v>
+        <v>-0.006772357970476151</v>
       </c>
       <c r="JB55" t="n">
         <v>0.1199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.01526877656579018</v>
+        <v>-0.01594405248761177</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.02000000000000007</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.009026631712913513</v>
+        <v>0.008603844791650772</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.02000000000000007</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.04134514555335045</v>
+        <v>-0.04196884855628014</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.02000000000000007</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.03339111432433128</v>
+        <v>-0.04010402783751488</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.001816079020500183</v>
+        <v>0.001135729253292084</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.02000000000000007</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003373067826032639</v>
+        <v>-0.003993581980466843</v>
       </c>
       <c r="JB61" t="n">
         <v>0.7199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.02251827344298363</v>
+        <v>-0.02324849739670753</v>
       </c>
       <c r="JB62" t="n">
         <v>0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.02007193490862846</v>
+        <v>-0.02083780243992805</v>
       </c>
       <c r="JB63" t="n">
         <v>0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.01400273665785789</v>
+        <v>-0.01160607114434242</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.06228164210915565</v>
+        <v>-0.06189268454909325</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.07285945117473602</v>
+        <v>-0.07333457469940186</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.06370654702186584</v>
+        <v>-0.06420508027076721</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>4.989784136234967</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0455504022538662</v>
+        <v>-0.06032947823405266</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>4.989784166547369</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.01346650347113609</v>
+        <v>-0.01186080649495125</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
         <v>4.989783977094859</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.006745383143424988</v>
+        <v>-0.007523387670516968</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7199999999999999</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
         <v>4.989784030141562</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.006663687527179718</v>
+        <v>0.006108440458774567</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>4.989784083188264</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.0008146762847900391</v>
+        <v>-0.001341044902801514</v>
       </c>
       <c r="JB72" t="n">
         <v>0.8599999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.01451227441430092</v>
+        <v>-0.01511453464627266</v>
       </c>
       <c r="JB73" t="n">
         <v>0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.01525947079062462</v>
+        <v>-0.01588191464543343</v>
       </c>
       <c r="JB74" t="n">
         <v>0.5799999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.008551470935344696</v>
+        <v>-0.009137962013483047</v>
       </c>
       <c r="JB75" t="n">
         <v>0.5799999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.004303105175495148</v>
+        <v>-0.004885662347078323</v>
       </c>
       <c r="JB76" t="n">
         <v>0.5799999999999998</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.007537800818681717</v>
+        <v>0.007089819759130478</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.16</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>4.98978361334604</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.004317298531532288</v>
+        <v>-0.00490700826048851</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="JC78" t="n">
         <v>4.98978361334604</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.02293415740132332</v>
+        <v>-0.0236169807612896</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1600000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
         <v>4.989783431471631</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.02588210627436638</v>
+        <v>-0.02660045400261879</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>4.989783598189839</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.0002718828618526459</v>
+        <v>-0.0008607357740402222</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
         <v>4.98978379522045</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.004726890474557877</v>
+        <v>0.004277225583791733</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.4399999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.01494292542338371</v>
+        <v>-0.01560812070965767</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.16</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.0421680323779583</v>
+        <v>-0.04300684109330177</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.1600000000000001</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.00518205389380455</v>
+        <v>-0.005798634141683578</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.006607722491025925</v>
+        <v>0.006107013672590256</v>
       </c>
       <c r="JB86" t="n">
         <v>0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.005217641592025757</v>
+        <v>0.004722408950328827</v>
       </c>
       <c r="JB87" t="n">
         <v>0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003978181630373001</v>
+        <v>-0.004519697278738022</v>
       </c>
       <c r="JB88" t="n">
         <v>0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.03644482418894768</v>
+        <v>-0.03721467033028603</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.01816165074706078</v>
+        <v>-0.01883620396256447</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002157367765903473</v>
+        <v>-0.002704992890357971</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.02815261110663414</v>
+        <v>-0.02885258570313454</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.001547202467918396</v>
+        <v>-0.002094969153404236</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.04984831437468529</v>
+        <v>-0.05082576349377632</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.01966977491974831</v>
+        <v>-0.020537119358778</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.16</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.01001979410648346</v>
+        <v>-0.01068723574280739</v>
       </c>
       <c r="JB96" t="n">
         <v>0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.01591142266988754</v>
+        <v>0.01542384549975395</v>
       </c>
       <c r="JB97" t="n">
         <v>0.5799999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.01250101253390312</v>
+        <v>0.01203624159097672</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.006860498338937759</v>
+        <v>-0.007471784949302673</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.002010758966207504</v>
+        <v>0.001450460404157639</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.01718297228217125</v>
+        <v>0.01671712473034859</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.006900142878293991</v>
+        <v>0.00644930824637413</v>
       </c>
       <c r="JB102" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.03814482316374779</v>
+        <v>-0.03899437561631203</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.01467718929052353</v>
+        <v>0.01414128392934799</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.16</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.00669398158788681</v>
+        <v>0.006217774003744125</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>3.174319863319397e-05</v>
+        <v>-0.0004981346428394318</v>
       </c>
       <c r="JB106" t="n">
         <v>0.1199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.004581909626722336</v>
+        <v>-0.005179990082979202</v>
       </c>
       <c r="JB107" t="n">
         <v>0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.0129743367433548</v>
+        <v>0.01254541426897049</v>
       </c>
       <c r="JB108" t="n">
         <v>0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.02671688608825207</v>
+        <v>0.02624955214560032</v>
       </c>
       <c r="JB109" t="n">
         <v>0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.02534761279821396</v>
+        <v>0.02483801171183586</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.01801422983407974</v>
+        <v>0.01747635379433632</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0169435515999794</v>
+        <v>0.01650843769311905</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.01825009286403656</v>
+        <v>0.01780248060822487</v>
       </c>
       <c r="JB113" t="n">
         <v>0.8599999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.02937855571508408</v>
+        <v>0.02887065336108208</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.02354414388537407</v>
+        <v>0.02305350825190544</v>
       </c>
       <c r="JB115" t="n">
         <v>0.1199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.01849814876914024</v>
+        <v>0.01803186908364296</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.02000000000000007</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.01562341675162315</v>
+        <v>0.01512435078620911</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.01121670007705688</v>
+        <v>0.01070151850581169</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.16</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.01570022851228714</v>
+        <v>0.01527407392859459</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.02089432999491692</v>
+        <v>0.0204368568956852</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.02230215072631836</v>
+        <v>0.0218249149620533</v>
       </c>
       <c r="JB121" t="n">
         <v>0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.0207916833460331</v>
+        <v>0.02029458805918694</v>
       </c>
       <c r="JB122" t="n">
         <v>0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.01999262720346451</v>
+        <v>0.01951989531517029</v>
       </c>
       <c r="JB123" t="n">
         <v>0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.01728371158242226</v>
+        <v>0.01683134958148003</v>
       </c>
       <c r="JB124" t="n">
         <v>0.8599999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.01271422207355499</v>
+        <v>0.01218084245920181</v>
       </c>
       <c r="JB125" t="n">
         <v>0.7899999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.03012174367904663</v>
+        <v>0.02955199778079987</v>
       </c>
       <c r="JB126" t="n">
         <v>0.7199999999999999</v>
